--- a/employee_evaluation_forms/033_probationary_evaluation_form--employee_evaluation_forms.xlsx
+++ b/employee_evaluation_forms/033_probationary_evaluation_form--employee_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>support_for_success</t>
+          <t>support_for_success_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>How have you received support for your success in your new role?</t>
+          <t>Support For Success 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>job_satisfaction_reason</t>
+          <t>job_satisfaction_reason_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Why are you satisfied or dissatisfied with your new job?</t>
+          <t>Job Satisfaction Reason 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>overall_feeling</t>
+          <t>overall_feeling_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Overall, how do you feel about your new role?</t>
+          <t>Overall Feeling 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>How will your employment status change in the next 6-12 months?</t>
+          <t>New Employment Status Change Two</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>What is your reason for the expected change in employment status?</t>
+          <t>Reason For Change Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>How would you describe communication with your colleagues?</t>
+          <t>Communication With Colleagues Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -985,7 +985,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>How would you describe your team's collaboration?</t>
+          <t>Team Work Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>How would you describe your job description?</t>
+          <t>Job Description Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>What are you expecting from your new role?</t>
+          <t>New Role Expectation Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>How have you received support for your success in your new role?</t>
+          <t>Support For Success Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
